--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="116">
   <si>
     <t>外观ID</t>
   </si>
@@ -275,6 +275,111 @@
   </si>
   <si>
     <t>野兽种族保底外形</t>
+  </si>
+  <si>
+    <t>App_0_01</t>
+  </si>
+  <si>
+    <t>基础兵种</t>
+  </si>
+  <si>
+    <t>App_0_11</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>App_0_21</t>
+  </si>
+  <si>
+    <t>App_0_31</t>
+  </si>
+  <si>
+    <t>App_0_02</t>
+  </si>
+  <si>
+    <t>近卫</t>
+  </si>
+  <si>
+    <t>高防御战士</t>
+  </si>
+  <si>
+    <t>App_0_12</t>
+  </si>
+  <si>
+    <t>炸弹师</t>
+  </si>
+  <si>
+    <t>范围爆炸</t>
+  </si>
+  <si>
+    <t>App_0_22</t>
+  </si>
+  <si>
+    <t>冰法</t>
+  </si>
+  <si>
+    <t>减速冰冻</t>
+  </si>
+  <si>
+    <t>App_0_32</t>
+  </si>
+  <si>
+    <t>格斗师</t>
+  </si>
+  <si>
+    <t>专供精英敌人</t>
+  </si>
+  <si>
+    <t>App_0_03</t>
+  </si>
+  <si>
+    <t>高伤害</t>
+  </si>
+  <si>
+    <t>App_0_13</t>
+  </si>
+  <si>
+    <t>长弓手</t>
+  </si>
+  <si>
+    <t>直线贯穿</t>
+  </si>
+  <si>
+    <t>App_0_23</t>
+  </si>
+  <si>
+    <t>火法</t>
+  </si>
+  <si>
+    <t>范围持续伤害</t>
+  </si>
+  <si>
+    <t>App_0_33</t>
+  </si>
+  <si>
+    <t>影刃</t>
+  </si>
+  <si>
+    <t>瞬移后排</t>
+  </si>
+  <si>
+    <t>App_4_41</t>
+  </si>
+  <si>
+    <t>圣骑士</t>
+  </si>
+  <si>
+    <t>范围防御</t>
+  </si>
+  <si>
+    <t>App_5_51</t>
+  </si>
+  <si>
+    <t>暗黑法师</t>
+  </si>
+  <si>
+    <t>致命魔法</t>
   </si>
 </sst>
 </file>
@@ -447,7 +552,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -457,6 +562,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -777,7 +894,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -801,16 +918,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -819,92 +936,100 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1288,7 +1413,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -1380,10 +1505,10 @@
       <c r="G3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J3" s="1" t="s">
@@ -1391,579 +1516,1048 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G4">
-        <v>0.16</v>
-      </c>
-      <c r="H4">
-        <v>0.5</v>
-      </c>
-      <c r="I4">
-        <v>0.5</v>
-      </c>
-      <c r="J4">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G5">
-        <v>0.16</v>
-      </c>
-      <c r="H5">
-        <v>0.5</v>
-      </c>
-      <c r="I5">
-        <v>0.5</v>
-      </c>
-      <c r="J5">
+      <c r="F5" s="3"/>
+      <c r="G5" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J5" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G6">
-        <v>0.16</v>
-      </c>
-      <c r="H6">
-        <v>0.5</v>
-      </c>
-      <c r="I6">
-        <v>0.5</v>
-      </c>
-      <c r="J6">
+      <c r="F6" s="3"/>
+      <c r="G6" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J6" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="3">
         <v>3</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G7">
-        <v>0.16</v>
-      </c>
-      <c r="H7">
-        <v>0.5</v>
-      </c>
-      <c r="I7">
-        <v>0.5</v>
-      </c>
-      <c r="J7">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J7" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="3">
         <v>2</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G8">
-        <v>0.16</v>
-      </c>
-      <c r="H8">
-        <v>0.5</v>
-      </c>
-      <c r="I8">
-        <v>0.5</v>
-      </c>
-      <c r="J8">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J8" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G9">
-        <v>0.16</v>
-      </c>
-      <c r="H9">
-        <v>0.5</v>
-      </c>
-      <c r="I9">
-        <v>0.5</v>
-      </c>
-      <c r="J9">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J9" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G10">
-        <v>0.16</v>
-      </c>
-      <c r="H10">
-        <v>0.5</v>
-      </c>
-      <c r="I10">
-        <v>0.5</v>
-      </c>
-      <c r="J10">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J10" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="3">
         <v>4</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G11">
-        <v>0.16</v>
-      </c>
-      <c r="H11">
-        <v>0.5</v>
-      </c>
-      <c r="I11">
-        <v>0.5</v>
-      </c>
-      <c r="J11">
+      <c r="F11" s="3"/>
+      <c r="G11" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J11" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="3">
         <v>3</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G12">
-        <v>0.16</v>
-      </c>
-      <c r="H12">
-        <v>0.5</v>
-      </c>
-      <c r="I12">
-        <v>0.5</v>
-      </c>
-      <c r="J12">
+      <c r="F12" s="3"/>
+      <c r="G12" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J12" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="3">
         <v>2</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E13" t="s">
+      <c r="D13" s="3"/>
+      <c r="E13" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G13">
-        <v>0.16</v>
-      </c>
-      <c r="H13">
-        <v>0.5</v>
-      </c>
-      <c r="I13">
-        <v>0.5</v>
-      </c>
-      <c r="J13">
+      <c r="F13" s="3"/>
+      <c r="G13" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J13" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" t="s">
+      <c r="A14" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E14" t="s">
+      <c r="D14" s="3"/>
+      <c r="E14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>0.16</v>
-      </c>
-      <c r="H14">
-        <v>0.5</v>
-      </c>
-      <c r="I14">
-        <v>0.5</v>
-      </c>
-      <c r="J14">
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J14" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E15" t="s">
+      <c r="D15" s="3"/>
+      <c r="E15" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>0.16</v>
-      </c>
-      <c r="H15">
-        <v>0.5</v>
-      </c>
-      <c r="I15">
-        <v>0.5</v>
-      </c>
-      <c r="J15">
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J15" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="B16" s="3">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E16" t="s">
+      <c r="D16" s="3"/>
+      <c r="E16" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>0.16</v>
-      </c>
-      <c r="H16">
-        <v>0.5</v>
-      </c>
-      <c r="I16">
-        <v>0.5</v>
-      </c>
-      <c r="J16">
+      <c r="F16" s="3">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J16" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E17" t="s">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17">
-        <v>0.16</v>
-      </c>
-      <c r="H17">
-        <v>0.5</v>
-      </c>
-      <c r="I17">
-        <v>0.5</v>
-      </c>
-      <c r="J17">
+      <c r="F17" s="3">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J17" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E18" t="s">
+      <c r="D18" s="3"/>
+      <c r="E18" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>0.16</v>
-      </c>
-      <c r="H18">
-        <v>0.5</v>
-      </c>
-      <c r="I18">
-        <v>0.5</v>
-      </c>
-      <c r="J18">
+      <c r="F18" s="3">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J18" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E19" t="s">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>0.16</v>
-      </c>
-      <c r="H19">
-        <v>0.5</v>
-      </c>
-      <c r="I19">
-        <v>0.5</v>
-      </c>
-      <c r="J19">
+      <c r="F19" s="3">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J19" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" t="s">
+      <c r="A20" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="B20" s="3">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E20" t="s">
+      <c r="D20" s="3"/>
+      <c r="E20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>0.16</v>
-      </c>
-      <c r="H20">
-        <v>0.5</v>
-      </c>
-      <c r="I20">
-        <v>0.5</v>
-      </c>
-      <c r="J20">
+      <c r="F20" s="3">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J20" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" t="s">
+      <c r="A21" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E21" t="s">
+      <c r="D21" s="3"/>
+      <c r="E21" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21">
-        <v>0.16</v>
-      </c>
-      <c r="H21">
-        <v>0.5</v>
-      </c>
-      <c r="I21">
-        <v>0.5</v>
-      </c>
-      <c r="J21">
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J21" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" t="s">
+      <c r="A22" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="B22" s="3">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E22" t="s">
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>0.16</v>
-      </c>
-      <c r="H22">
-        <v>0.5</v>
-      </c>
-      <c r="I22">
-        <v>0.5</v>
-      </c>
-      <c r="J22">
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J22" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" t="s">
+      <c r="A23" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="B23" s="3">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E23" t="s">
+      <c r="D23" s="3"/>
+      <c r="E23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>0.16</v>
-      </c>
-      <c r="H23">
-        <v>0.5</v>
-      </c>
-      <c r="I23">
-        <v>0.5</v>
-      </c>
-      <c r="J23">
+      <c r="F23" s="3">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" t="s">
+        <v>82</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="H24" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="I24" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J24" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="H25" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="I25" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J25" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="H26" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="I26" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J26" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="H27" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="I27" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J27" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" t="s">
+        <v>89</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="H28" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="I28" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J28" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="H29" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="I29" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J29" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" t="s">
+        <v>95</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="H30" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="I30" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J30" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="H31" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="I31" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J31" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" t="s">
+        <v>100</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="H32" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="I32" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J32" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="H33" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="I33" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J33" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34" t="s">
+        <v>47</v>
+      </c>
+      <c r="D34" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="H34" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="I34" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J34" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" t="s">
+        <v>108</v>
+      </c>
+      <c r="E35" t="s">
+        <v>109</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="H35" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="I35" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J35" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E36" t="s">
+        <v>112</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="H36" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="I36" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J36" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" t="s">
+        <v>114</v>
+      </c>
+      <c r="E37" t="s">
+        <v>115</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="H37" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="I37" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J37" s="6">
         <v>0</v>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="124">
   <si>
     <t>外观ID</t>
   </si>
@@ -277,22 +277,46 @@
     <t>野兽种族保底外形</t>
   </si>
   <si>
+    <t>App_0_00</t>
+  </si>
+  <si>
+    <t>基础兵种</t>
+  </si>
+  <si>
+    <t>App_0_10</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>App_0_20</t>
+  </si>
+  <si>
+    <t>App_0_30</t>
+  </si>
+  <si>
     <t>App_0_01</t>
   </si>
   <si>
-    <t>基础兵种</t>
+    <t>2级战士</t>
   </si>
   <si>
     <t>App_0_11</t>
   </si>
   <si>
-    <t>射手</t>
+    <t>2级射手</t>
   </si>
   <si>
     <t>App_0_21</t>
   </si>
   <si>
+    <t>2级法师</t>
+  </si>
+  <si>
     <t>App_0_31</t>
+  </si>
+  <si>
+    <t>2级盗贼</t>
   </si>
   <si>
     <t>App_0_02</t>
@@ -552,18 +576,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -894,7 +912,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -918,16 +936,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -936,94 +954,93 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1413,7 +1430,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -1505,10 +1522,10 @@
       <c r="G3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="J3" s="1" t="s">
@@ -1516,605 +1533,605 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J4" s="3">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J5" s="3">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>2</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="F6" s="2"/>
+      <c r="G6" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>3</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J7" s="3">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>2</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J8" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>3</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J10" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>4</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J11" s="3">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J11" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>3</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J12" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <v>2</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3" t="s">
+      <c r="D13" s="2"/>
+      <c r="E13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H13" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I13" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J13" s="3">
+      <c r="F13" s="2"/>
+      <c r="G13" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J13" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="3">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3" t="s">
+      <c r="D14" s="2"/>
+      <c r="E14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="3">
-        <v>1</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J14" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="3">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3" t="s">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="3">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J15" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="3">
-        <v>1</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3" t="s">
+      <c r="D16" s="2"/>
+      <c r="E16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F16" s="3">
-        <v>1</v>
-      </c>
-      <c r="G16" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I16" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J16" s="3">
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J16" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="3">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="B17" s="2">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3" t="s">
+      <c r="D17" s="2"/>
+      <c r="E17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="3">
-        <v>1</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J17" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="3">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="B18" s="2">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3" t="s">
+      <c r="D18" s="2"/>
+      <c r="E18" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="3">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J18" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="3">
-        <v>1</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="B19" s="2">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3" t="s">
+      <c r="D19" s="2"/>
+      <c r="E19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F19" s="3">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I19" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J19" s="3">
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J19" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="3">
-        <v>1</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="B20" s="2">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3" t="s">
+      <c r="D20" s="2"/>
+      <c r="E20" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F20" s="3">
-        <v>1</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J20" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="3">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="B21" s="2">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3" t="s">
+      <c r="D21" s="2"/>
+      <c r="E21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F21" s="3">
-        <v>1</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J21" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="3">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="B22" s="2">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3" t="s">
+      <c r="D22" s="2"/>
+      <c r="E22" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F22" s="3">
-        <v>1</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J22" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="3">
-        <v>1</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3" t="s">
+      <c r="D23" s="2"/>
+      <c r="E23" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F23" s="3">
-        <v>1</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0.16</v>
-      </c>
-      <c r="H23" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="I23" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J23" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>81</v>
       </c>
       <c r="B24">
@@ -2132,21 +2149,21 @@
       <c r="F24">
         <v>1</v>
       </c>
-      <c r="G24" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="H24" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="I24" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J24" s="6">
+      <c r="G24" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="H24" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="I24" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="J24" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B25">
@@ -2164,21 +2181,21 @@
       <c r="F25">
         <v>1</v>
       </c>
-      <c r="G25" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="H25" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="I25" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J25" s="6">
+      <c r="G25" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="H25" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="I25" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="J25" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>85</v>
       </c>
       <c r="B26">
@@ -2196,21 +2213,21 @@
       <c r="F26">
         <v>1</v>
       </c>
-      <c r="G26" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="H26" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="I26" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J26" s="6">
+      <c r="G26" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="H26" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="I26" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="J26" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B27">
@@ -2228,336 +2245,464 @@
       <c r="F27">
         <v>1</v>
       </c>
-      <c r="G27" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="H27" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="I27" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J27" s="6">
+      <c r="G27" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="H27" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="I27" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="J27" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="4">
         <v>2</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" s="4">
+        <v>1</v>
+      </c>
+      <c r="G28" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="H28" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="I28" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="J28" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="H28" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="I28" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J28" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="5" t="s">
+      <c r="B29" s="4">
+        <v>2</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B29">
+      <c r="F29" s="4">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="H29" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="I29" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="J29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="4">
         <v>2</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="D30" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="H29" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="I29" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J29" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="5" t="s">
+      <c r="F30" s="4">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="H30" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="I30" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="J30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B30">
+      <c r="B31" s="4">
         <v>2</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F31" s="4">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="H31" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="J31" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="H30" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="I30" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J30" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="5" t="s">
+      <c r="B32" s="4">
+        <v>3</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B31">
-        <v>2</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="E32" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F32" s="4">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="H32" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I32" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J32" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="4">
+        <v>3</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D31" t="s">
-        <v>97</v>
-      </c>
-      <c r="E31" t="s">
-        <v>98</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="H31" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="I31" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J31" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="5" t="s">
+      <c r="D33" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B32">
-        <v>2</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="E33" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F33" s="4">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="H33" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I33" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J33" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="4">
+        <v>3</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D34" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F34" s="4">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="H34" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I34" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J34" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" s="4">
+        <v>3</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F35" s="4">
+        <v>1</v>
+      </c>
+      <c r="G35" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="H35" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I35" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J35" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="4">
+        <v>3</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E32" t="s">
-        <v>100</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="H32" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="I32" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J32" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B33">
-        <v>2</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="E36" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F36" s="4">
+        <v>1</v>
+      </c>
+      <c r="G36" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="H36" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I36" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J36" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="4">
+        <v>3</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D33" t="s">
-        <v>102</v>
-      </c>
-      <c r="E33" t="s">
-        <v>103</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="H33" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="I33" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J33" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34">
-        <v>2</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="D37" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F37" s="4">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="H37" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I37" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J37" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="4">
+        <v>3</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D34" t="s">
-        <v>105</v>
-      </c>
-      <c r="E34" t="s">
-        <v>106</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="H34" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="I34" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J34" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B35">
-        <v>2</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="D38" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F38" s="4">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="H38" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I38" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J38" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="4">
+        <v>3</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D35" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" t="s">
-        <v>109</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="G35" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="H35" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="I35" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J35" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B36">
-        <v>3</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="D39" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F39" s="4">
+        <v>1</v>
+      </c>
+      <c r="G39" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="H39" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I39" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J39" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="4">
+        <v>4</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D36" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="E36" t="s">
-        <v>112</v>
-      </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-      <c r="G36" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="H36" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="I36" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J36" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B37">
-        <v>3</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="D40" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F40" s="4">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="H40" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="I40" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="J40" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="4">
+        <v>4</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D37" t="s">
-        <v>114</v>
-      </c>
-      <c r="E37" t="s">
-        <v>115</v>
-      </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-      <c r="G37" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="H37" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="I37" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="J37" s="6">
+      <c r="D41" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F41" s="4">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="H41" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="I41" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="J41" s="4">
         <v>0</v>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
@@ -31,8 +31,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>JM</author>
+  </authors>
+  <commentList>
+    <comment ref="D2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>JM:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+这个“职业”如果相同，则会出现外形随机</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="84">
   <si>
     <t>外观ID</t>
   </si>
@@ -124,280 +156,160 @@
     <t>FacingYawFlip</t>
   </si>
   <si>
-    <t>App_01</t>
-  </si>
-  <si>
-    <t>Race_Human</t>
-  </si>
-  <si>
-    <t>骑士|战士</t>
-  </si>
-  <si>
-    <t>人类战士外观</t>
-  </si>
-  <si>
-    <t>App_02</t>
-  </si>
-  <si>
-    <t>Race_Construct</t>
+    <t>App_0_00</t>
+  </si>
+  <si>
+    <t>Race_Undead</t>
+  </si>
+  <si>
+    <t>枯骨战士</t>
+  </si>
+  <si>
+    <t>基础兵种</t>
+  </si>
+  <si>
+    <t>App_0_10</t>
+  </si>
+  <si>
+    <t>枯骨射手</t>
+  </si>
+  <si>
+    <t>App_0_20</t>
+  </si>
+  <si>
+    <t>枯骨法师</t>
+  </si>
+  <si>
+    <t>App_0_30</t>
+  </si>
+  <si>
+    <t>枯骨刺客</t>
+  </si>
+  <si>
+    <t>App_0_01</t>
   </si>
   <si>
     <t>战士</t>
   </si>
   <si>
-    <t>构造体保底外形</t>
-  </si>
-  <si>
-    <t>App_03</t>
-  </si>
-  <si>
-    <t>Race_Elf</t>
-  </si>
-  <si>
-    <t>射手|游侠</t>
-  </si>
-  <si>
-    <t>精灵远程外观</t>
-  </si>
-  <si>
-    <t>App_04</t>
-  </si>
-  <si>
-    <t>Race_Orc</t>
+    <t>2级战士</t>
+  </si>
+  <si>
+    <t>App_0_11</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>2级射手</t>
+  </si>
+  <si>
+    <t>App_0_21</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>2级法师</t>
+  </si>
+  <si>
+    <t>App_0_31</t>
+  </si>
+  <si>
+    <t>刺客</t>
+  </si>
+  <si>
+    <t>2级刺客</t>
+  </si>
+  <si>
+    <t>App_0_02</t>
+  </si>
+  <si>
+    <t>近卫</t>
+  </si>
+  <si>
+    <t>高防御战士</t>
+  </si>
+  <si>
+    <t>App_0_12</t>
+  </si>
+  <si>
+    <t>炸弹师</t>
+  </si>
+  <si>
+    <t>范围爆炸</t>
+  </si>
+  <si>
+    <t>App_0_22</t>
+  </si>
+  <si>
+    <t>冰法</t>
+  </si>
+  <si>
+    <t>减速冰冻</t>
+  </si>
+  <si>
+    <t>App_0_32</t>
+  </si>
+  <si>
+    <t>格斗师</t>
+  </si>
+  <si>
+    <t>专供精英敌人</t>
+  </si>
+  <si>
+    <t>App_0_03</t>
   </si>
   <si>
     <t>狂战士</t>
   </si>
   <si>
-    <t>兽人蛮力外观</t>
-  </si>
-  <si>
-    <t>App_05</t>
-  </si>
-  <si>
-    <t>Race_Undead</t>
-  </si>
-  <si>
-    <t>法师</t>
-  </si>
-  <si>
-    <t>亡灵施法外观</t>
-  </si>
-  <si>
-    <t>App_06</t>
-  </si>
-  <si>
-    <t>Race_Dwarf</t>
-  </si>
-  <si>
-    <t>骑士|圣骑士</t>
-  </si>
-  <si>
-    <t>矮人重装外观</t>
-  </si>
-  <si>
-    <t>App_07</t>
-  </si>
-  <si>
-    <t>Race_Goblin</t>
-  </si>
-  <si>
-    <t>盗贼</t>
-  </si>
-  <si>
-    <t>哥布林外观</t>
-  </si>
-  <si>
-    <t>App_08</t>
+    <t>高伤害</t>
+  </si>
+  <si>
+    <t>App_0_13</t>
+  </si>
+  <si>
+    <t>长弓手</t>
+  </si>
+  <si>
+    <t>直线贯穿</t>
+  </si>
+  <si>
+    <t>App_0_23</t>
+  </si>
+  <si>
+    <t>火法</t>
+  </si>
+  <si>
+    <t>范围持续伤害</t>
+  </si>
+  <si>
+    <t>App_0_33</t>
+  </si>
+  <si>
+    <t>影刃</t>
+  </si>
+  <si>
+    <t>瞬移后排</t>
+  </si>
+  <si>
+    <t>App_4_41</t>
+  </si>
+  <si>
+    <t>Race_Angel</t>
+  </si>
+  <si>
+    <t>圣骑士</t>
+  </si>
+  <si>
+    <t>范围防御</t>
+  </si>
+  <si>
+    <t>App_5_51</t>
   </si>
   <si>
     <t>Race_Demon</t>
-  </si>
-  <si>
-    <t>术士</t>
-  </si>
-  <si>
-    <t>恶魔外观</t>
-  </si>
-  <si>
-    <t>App_09</t>
-  </si>
-  <si>
-    <t>Race_Angel</t>
-  </si>
-  <si>
-    <t>牧师</t>
-  </si>
-  <si>
-    <t>天使外观</t>
-  </si>
-  <si>
-    <t>App_10</t>
-  </si>
-  <si>
-    <t>Race_Beast</t>
-  </si>
-  <si>
-    <t>野兽外观</t>
-  </si>
-  <si>
-    <t>App_90</t>
-  </si>
-  <si>
-    <t>App_91</t>
-  </si>
-  <si>
-    <t>种族保底外形</t>
-  </si>
-  <si>
-    <t>App_92</t>
-  </si>
-  <si>
-    <t>App_93</t>
-  </si>
-  <si>
-    <t>App_94</t>
-  </si>
-  <si>
-    <t>App_95</t>
-  </si>
-  <si>
-    <t>App_96</t>
-  </si>
-  <si>
-    <t>App_97</t>
-  </si>
-  <si>
-    <t>App_98</t>
-  </si>
-  <si>
-    <t>App_99</t>
-  </si>
-  <si>
-    <t>野兽种族保底外形</t>
-  </si>
-  <si>
-    <t>App_0_00</t>
-  </si>
-  <si>
-    <t>基础兵种</t>
-  </si>
-  <si>
-    <t>App_0_10</t>
-  </si>
-  <si>
-    <t>射手</t>
-  </si>
-  <si>
-    <t>App_0_20</t>
-  </si>
-  <si>
-    <t>App_0_30</t>
-  </si>
-  <si>
-    <t>App_0_01</t>
-  </si>
-  <si>
-    <t>2级战士</t>
-  </si>
-  <si>
-    <t>App_0_11</t>
-  </si>
-  <si>
-    <t>2级射手</t>
-  </si>
-  <si>
-    <t>App_0_21</t>
-  </si>
-  <si>
-    <t>2级法师</t>
-  </si>
-  <si>
-    <t>App_0_31</t>
-  </si>
-  <si>
-    <t>2级盗贼</t>
-  </si>
-  <si>
-    <t>App_0_02</t>
-  </si>
-  <si>
-    <t>近卫</t>
-  </si>
-  <si>
-    <t>高防御战士</t>
-  </si>
-  <si>
-    <t>App_0_12</t>
-  </si>
-  <si>
-    <t>炸弹师</t>
-  </si>
-  <si>
-    <t>范围爆炸</t>
-  </si>
-  <si>
-    <t>App_0_22</t>
-  </si>
-  <si>
-    <t>冰法</t>
-  </si>
-  <si>
-    <t>减速冰冻</t>
-  </si>
-  <si>
-    <t>App_0_32</t>
-  </si>
-  <si>
-    <t>格斗师</t>
-  </si>
-  <si>
-    <t>专供精英敌人</t>
-  </si>
-  <si>
-    <t>App_0_03</t>
-  </si>
-  <si>
-    <t>高伤害</t>
-  </si>
-  <si>
-    <t>App_0_13</t>
-  </si>
-  <si>
-    <t>长弓手</t>
-  </si>
-  <si>
-    <t>直线贯穿</t>
-  </si>
-  <si>
-    <t>App_0_23</t>
-  </si>
-  <si>
-    <t>火法</t>
-  </si>
-  <si>
-    <t>范围持续伤害</t>
-  </si>
-  <si>
-    <t>App_0_33</t>
-  </si>
-  <si>
-    <t>影刃</t>
-  </si>
-  <si>
-    <t>瞬移后排</t>
-  </si>
-  <si>
-    <t>App_4_41</t>
-  </si>
-  <si>
-    <t>圣骑士</t>
-  </si>
-  <si>
-    <t>范围防御</t>
-  </si>
-  <si>
-    <t>App_5_51</t>
   </si>
   <si>
     <t>暗黑法师</t>
@@ -416,7 +328,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -575,8 +487,19 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -586,12 +509,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -912,7 +829,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -936,16 +853,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -954,93 +871,91 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1430,7 +1345,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -1536,29 +1451,31 @@
       <c r="A4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2">
-        <v>0.16</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="J4" s="2">
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="J4" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1566,109 +1483,117 @@
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="2">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2">
-        <v>0.16</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="J5" s="2">
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="J5" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="2">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2">
-        <v>0.16</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="J6" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="J6" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="2">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2">
-        <v>0.16</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="J7" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="J7" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B8" s="2">
         <v>2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
       <c r="G8" s="2">
         <v>0.16</v>
       </c>
@@ -1684,21 +1609,23 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
       <c r="G9" s="2">
         <v>0.16</v>
       </c>
@@ -1714,21 +1641,23 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
       <c r="G10" s="2">
         <v>0.16</v>
       </c>
@@ -1744,21 +1673,23 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
       <c r="G11" s="2">
         <v>0.16</v>
       </c>
@@ -1774,29 +1705,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2">
         <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>64</v>
+        <v>31</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
       <c r="G12" s="2">
         <v>0.16</v>
       </c>
       <c r="H12" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I12" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J12" s="2">
         <v>0</v>
@@ -1804,27 +1737,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="E13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
       <c r="G13" s="2">
         <v>0.16</v>
       </c>
       <c r="H13" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I13" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J13" s="2">
         <v>0</v>
@@ -1832,17 +1769,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="E14" s="2" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
@@ -1851,10 +1790,10 @@
         <v>0.16</v>
       </c>
       <c r="H14" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I14" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J14" s="2">
         <v>0</v>
@@ -1862,17 +1801,19 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="E15" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -1881,10 +1822,10 @@
         <v>0.16</v>
       </c>
       <c r="H15" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I15" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J15" s="2">
         <v>0</v>
@@ -1892,17 +1833,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B16" s="2">
-        <v>1</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="E16" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
@@ -1911,10 +1854,10 @@
         <v>0.16</v>
       </c>
       <c r="H16" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I16" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J16" s="2">
         <v>0</v>
@@ -1922,17 +1865,19 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2">
-        <v>1</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="E17" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F17" s="2">
         <v>1</v>
@@ -1941,10 +1886,10 @@
         <v>0.16</v>
       </c>
       <c r="H17" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I17" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J17" s="2">
         <v>0</v>
@@ -1952,17 +1897,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2">
-        <v>1</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="E18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F18" s="2">
         <v>1</v>
@@ -1971,10 +1918,10 @@
         <v>0.16</v>
       </c>
       <c r="H18" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I18" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J18" s="2">
         <v>0</v>
@@ -1982,17 +1929,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="2">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="B19" s="2">
-        <v>1</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
@@ -2001,28 +1950,30 @@
         <v>0.16</v>
       </c>
       <c r="H19" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I19" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J19" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>76</v>
       </c>
       <c r="B20" s="2">
-        <v>1</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="E20" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F20" s="2">
         <v>1</v>
@@ -2031,28 +1982,30 @@
         <v>0.16</v>
       </c>
       <c r="H20" s="2">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="I20" s="2">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J20" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>77</v>
+      <c r="A21" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="B21" s="2">
-        <v>1</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E21" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F21" s="2">
         <v>1</v>
@@ -2061,648 +2014,12 @@
         <v>0.16</v>
       </c>
       <c r="H21" s="2">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="I21" s="2">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J21" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B22" s="2">
-        <v>1</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F22" s="2">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0.16</v>
-      </c>
-      <c r="H22" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="J22" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" s="2">
-        <v>1</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23" s="2">
-        <v>1</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0.16</v>
-      </c>
-      <c r="H23" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="J23" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" t="s">
-        <v>82</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="H24" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="I24" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="J24" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" t="s">
-        <v>82</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="H25" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="I25" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="J25" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" t="s">
-        <v>48</v>
-      </c>
-      <c r="E26" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="H26" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="I26" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="J26" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" t="s">
-        <v>56</v>
-      </c>
-      <c r="E27" t="s">
-        <v>82</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="H27" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="I27" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="J27" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" s="4">
-        <v>2</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F28" s="4">
-        <v>1</v>
-      </c>
-      <c r="G28" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="H28" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="I28" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="J28" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B29" s="4">
-        <v>2</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F29" s="4">
-        <v>1</v>
-      </c>
-      <c r="G29" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="H29" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="I29" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="J29" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B30" s="4">
-        <v>2</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F30" s="4">
-        <v>1</v>
-      </c>
-      <c r="G30" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="H30" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="I30" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="J30" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31" s="4">
-        <v>2</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F31" s="4">
-        <v>1</v>
-      </c>
-      <c r="G31" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="H31" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="I31" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="J31" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B32" s="4">
-        <v>3</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F32" s="4">
-        <v>1</v>
-      </c>
-      <c r="G32" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="H32" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="I32" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="J32" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B33" s="4">
-        <v>3</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F33" s="4">
-        <v>1</v>
-      </c>
-      <c r="G33" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="H33" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="I33" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="J33" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B34" s="4">
-        <v>3</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F34" s="4">
-        <v>1</v>
-      </c>
-      <c r="G34" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="H34" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="I34" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="J34" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B35" s="4">
-        <v>3</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F35" s="4">
-        <v>1</v>
-      </c>
-      <c r="G35" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="H35" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="I35" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="J35" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B36" s="4">
-        <v>3</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F36" s="4">
-        <v>1</v>
-      </c>
-      <c r="G36" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="H36" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="I36" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="J36" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B37" s="4">
-        <v>3</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F37" s="4">
-        <v>1</v>
-      </c>
-      <c r="G37" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="H37" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="I37" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="J37" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B38" s="4">
-        <v>3</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F38" s="4">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="H38" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="I38" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="J38" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B39" s="4">
-        <v>3</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="F39" s="4">
-        <v>1</v>
-      </c>
-      <c r="G39" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="H39" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="I39" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="J39" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B40" s="4">
-        <v>4</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="F40" s="4">
-        <v>1</v>
-      </c>
-      <c r="G40" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="H40" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="I40" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="J40" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B41" s="4">
-        <v>4</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F41" s="4">
-        <v>1</v>
-      </c>
-      <c r="G41" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="H41" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="I41" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="J41" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2710,5 +2027,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体外观配置表_Manufacture_BodyAppearanceConfig.xlsx
@@ -1127,7 +1127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="9" customWidth="1" style="6" min="2" max="2"/>
@@ -2253,7 +2253,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>App_1_33</t>
+          <t>App_1_32</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>影刃</t>
+          <t>格斗师</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>瞬移后排</t>
+          <t>专供精英敌人</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -2293,7 +2293,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>App_2_02</t>
+          <t>App_1_33</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Race_Elf</t>
+          <t>Race_Human</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>近卫</t>
+          <t>影刃</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>高防御战士</t>
+          <t>瞬移后排</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -2333,7 +2333,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>App_2_03</t>
+          <t>App_2_02</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>狂战士</t>
+          <t>近卫</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>高伤害</t>
+          <t>高防御战士</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -2373,7 +2373,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>App_2_12</t>
+          <t>App_2_03</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>炸弹师</t>
+          <t>狂战士</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>范围爆炸</t>
+          <t>高伤害</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2413,7 +2413,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>App_2_13</t>
+          <t>App_2_12</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>长弓手</t>
+          <t>炸弹师</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>直线贯穿</t>
+          <t>范围爆炸</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2453,7 +2453,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>App_2_22</t>
+          <t>App_2_13</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>冰法</t>
+          <t>长弓手</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>减速冰冻</t>
+          <t>直线贯穿</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2493,7 +2493,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>App_2_23</t>
+          <t>App_2_22</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>火法</t>
+          <t>冰法</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>范围持续伤害</t>
+          <t>减速冰冻</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -2533,7 +2533,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>App_2_32</t>
+          <t>App_2_23</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>格斗师</t>
+          <t>火法</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>专供精英敌人</t>
+          <t>范围持续伤害</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2573,7 +2573,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>App_2_33</t>
+          <t>App_2_32</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>影刃</t>
+          <t>格斗师</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>瞬移后排</t>
+          <t>专供精英敌人</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2613,7 +2613,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>App_3_02</t>
+          <t>App_2_33</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Race_Orc</t>
+          <t>Race_Elf</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>近卫</t>
+          <t>影刃</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>高防御战士</t>
+          <t>瞬移后排</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2653,7 +2653,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>App_3_03</t>
+          <t>App_3_02</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>狂战士</t>
+          <t>近卫</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>高伤害</t>
+          <t>高防御战士</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2693,7 +2693,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>App_3_12</t>
+          <t>App_3_03</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>炸弹师</t>
+          <t>狂战士</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>范围爆炸</t>
+          <t>高伤害</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2733,7 +2733,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>App_3_13</t>
+          <t>App_3_12</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>长弓手</t>
+          <t>炸弹师</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>直线贯穿</t>
+          <t>范围爆炸</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2773,7 +2773,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>App_3_22</t>
+          <t>App_3_13</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>冰法</t>
+          <t>长弓手</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>减速冰冻</t>
+          <t>直线贯穿</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -2813,7 +2813,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>App_3_23</t>
+          <t>App_3_22</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>火法</t>
+          <t>冰法</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>范围持续伤害</t>
+          <t>减速冰冻</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2853,7 +2853,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>App_3_32</t>
+          <t>App_3_23</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>格斗师</t>
+          <t>火法</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>专供精英敌人</t>
+          <t>范围持续伤害</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -2893,40 +2893,80 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>App_3_32</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Race_Orc</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>格斗师</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>专供精英敌人</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>App_3_33</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>3</v>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>Race_Orc</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>影刃</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>瞬移后排</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J44" t="n">
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J45" t="n">
         <v>0</v>
       </c>
     </row>
